--- a/Team-Data/2008-09/4-11-2008-09.xlsx
+++ b/Team-Data/2008-09/4-11-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -775,10 +842,10 @@
         <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
@@ -808,13 +875,13 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB2" t="n">
         <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -864,64 +931,64 @@
         <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.396</v>
+        <v>0.394</v>
       </c>
       <c r="O3" t="n">
         <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -948,7 +1015,7 @@
         <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -957,10 +1024,10 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -978,7 +1045,7 @@
         <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
         <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438</v>
+        <v>0.443</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1055,31 +1122,31 @@
         <v>16.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O4" t="n">
         <v>17.6</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T4" t="n">
         <v>39.7</v>
       </c>
       <c r="U4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1097,13 +1164,13 @@
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC4" t="n">
         <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,13 +1191,13 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN4" t="n">
         <v>14</v>
@@ -1148,10 +1215,10 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
@@ -1175,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1222,31 +1289,31 @@
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
@@ -1261,7 +1328,7 @@
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1270,22 +1337,22 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1312,13 +1379,13 @@
         <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1327,22 +1394,22 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1351,7 +1418,7 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,52 +1456,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.821</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.467</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
         <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
         <v>18.5</v>
       </c>
       <c r="P6" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T6" t="n">
         <v>42.1</v>
@@ -1443,7 +1510,7 @@
         <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,10 +1567,10 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
@@ -1518,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1679,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
         <v>2</v>
@@ -1703,10 +1770,10 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>10</v>
@@ -1873,7 +1940,7 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.488</v>
+        <v>0.494</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,10 +2020,10 @@
         <v>36.4</v>
       </c>
       <c r="J9" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
@@ -1965,16 +2032,16 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
         <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R9" t="n">
         <v>11.5</v>
@@ -1983,16 +2050,16 @@
         <v>29.8</v>
       </c>
       <c r="T9" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U9" t="n">
         <v>20.7</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X9" t="n">
         <v>4.6</v>
@@ -2007,25 +2074,25 @@
         <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2043,7 +2110,7 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
@@ -2079,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.363</v>
+        <v>0.354</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2135,10 +2202,10 @@
         <v>39.5</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
         <v>6.8</v>
@@ -2147,13 +2214,13 @@
         <v>18.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O10" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="P10" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0.792</v>
@@ -2174,7 +2241,7 @@
         <v>14.7</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X10" t="n">
         <v>6.4</v>
@@ -2183,19 +2250,19 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>109</v>
+        <v>108.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>14</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2249,7 +2316,7 @@
         <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2450,13 @@
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>24</v>
@@ -2422,16 +2489,16 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.438</v>
+        <v>0.43</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2511,7 +2578,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O12" t="n">
         <v>18.5</v>
@@ -2520,19 +2587,19 @@
         <v>22.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V12" t="n">
         <v>14.5</v>
@@ -2550,28 +2617,28 @@
         <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
         <v>104.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2589,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>21</v>
@@ -2604,16 +2671,16 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
         <v>23</v>
@@ -2628,13 +2695,13 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0.238</v>
+        <v>0.241</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2684,25 +2751,25 @@
         <v>81.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O13" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P13" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R13" t="n">
         <v>11</v>
@@ -2714,13 +2781,13 @@
         <v>40</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
         <v>5.9</v>
@@ -2735,13 +2802,13 @@
         <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2762,10 +2829,10 @@
         <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
@@ -2777,13 +2844,13 @@
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
         <v>23</v>
@@ -2792,10 +2859,10 @@
         <v>24</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,16 +2939,16 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
         <v>19.7</v>
       </c>
       <c r="P14" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.768</v>
@@ -2890,16 +2957,16 @@
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
@@ -2914,16 +2981,16 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2950,13 +3017,13 @@
         <v>16</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2989,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
@@ -3123,7 +3190,7 @@
         <v>30</v>
       </c>
       <c r="AJ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
@@ -3177,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3338,7 +3405,7 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -3394,19 +3461,19 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.418</v>
+        <v>0.405</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
         <v>82.2</v>
@@ -3418,34 +3485,34 @@
         <v>6.2</v>
       </c>
       <c r="M17" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3454,22 +3521,22 @@
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3490,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3505,16 +3572,16 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3523,10 +3590,10 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3544,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="n">
         <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.304</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,28 +3658,28 @@
         <v>36.5</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L18" t="n">
         <v>6.6</v>
       </c>
       <c r="M18" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P18" t="n">
         <v>24</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
         <v>11.9</v>
@@ -3648,10 +3715,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
         <v>21</v>
@@ -3672,19 +3739,19 @@
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
@@ -3693,28 +3760,28 @@
         <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
         <v>28</v>
       </c>
       <c r="AY18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -3755,49 +3822,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
         <v>21.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O19" t="n">
         <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S19" t="n">
         <v>29.5</v>
@@ -3806,13 +3873,13 @@
         <v>39.7</v>
       </c>
       <c r="U19" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V19" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W19" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
@@ -3827,25 +3894,25 @@
         <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3854,16 +3921,16 @@
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3875,13 +3942,13 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
@@ -3893,7 +3960,7 @@
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -3902,7 +3969,7 @@
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4027,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4042,7 +4109,7 @@
         <v>13</v>
       </c>
       <c r="AM20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN20" t="n">
         <v>17</v>
@@ -4051,7 +4118,7 @@
         <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4251,10 +4318,10 @@
         <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
         <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4328,16 +4395,16 @@
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O22" t="n">
         <v>19.8</v>
       </c>
       <c r="P22" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0.785</v>
@@ -4364,22 +4431,22 @@
         <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z22" t="n">
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB22" t="n">
         <v>96.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4391,10 +4458,10 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4436,16 +4503,16 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.725</v>
+        <v>0.734</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4504,13 +4571,13 @@
         <v>78.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L23" t="n">
         <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.382</v>
@@ -4522,22 +4589,22 @@
         <v>27.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="R23" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T23" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
         <v>7</v>
@@ -4555,13 +4622,13 @@
         <v>22.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>101.4</v>
+        <v>101.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4582,19 +4649,19 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4627,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4758,13 +4825,13 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4797,7 +4864,7 @@
         <v>23</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" t="n">
         <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.544</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4868,22 +4935,22 @@
         <v>81.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.504</v>
+        <v>0.505</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
         <v>17.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O25" t="n">
         <v>20.2</v>
       </c>
       <c r="P25" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q25" t="n">
         <v>0.745</v>
@@ -4892,16 +4959,16 @@
         <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>23.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W25" t="n">
         <v>7.1</v>
@@ -4922,10 +4989,10 @@
         <v>109.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>5</v>
@@ -4991,7 +5058,7 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>4</v>
@@ -5000,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -5032,55 +5099,55 @@
         <v>79</v>
       </c>
       <c r="E26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.658</v>
+        <v>0.646</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0.766</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T26" t="n">
         <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5098,31 +5165,31 @@
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF26" t="n">
         <v>6</v>
       </c>
-      <c r="AF26" t="n">
-        <v>5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
@@ -5176,7 +5243,7 @@
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5331,10 +5398,10 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>29</v>
@@ -5346,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5538,19 @@
         <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>7</v>
       </c>
-      <c r="AG28" t="n">
-        <v>8</v>
-      </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5680,16 +5747,16 @@
         <v>24</v>
       </c>
       <c r="AM29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN29" t="n">
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5710,10 +5777,10 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
         <v>47</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G30" t="n">
-        <v>0.588</v>
+        <v>0.595</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,7 +5842,7 @@
         <v>38.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.475</v>
@@ -5784,16 +5851,16 @@
         <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.771</v>
@@ -5802,7 +5869,7 @@
         <v>11.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
         <v>41</v>
@@ -5811,19 +5878,19 @@
         <v>24.7</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y30" t="n">
         <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
         <v>23.9</v>
@@ -5832,10 +5899,10 @@
         <v>103.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
@@ -5847,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5859,13 +5926,13 @@
         <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
@@ -5898,7 +5965,7 @@
         <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
@@ -6023,10 +6090,10 @@
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2008-09</t>
+          <t>2009-04-11</t>
         </is>
       </c>
     </row>
